--- a/research/17-teksty-ru-uz/для-носителя/Тексты на проверку — UZ.xlsx
+++ b/research/17-teksty-ru-uz/для-носителя/Тексты на проверку — UZ.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>Talaba bo‘lsangiz va internetda hali bir marta ham pul ishlamagan bo‘lsangiz, oyiga $1000 ga qanday chiqiladi?
+          <t>Talaba bo‘lsangiz va internetda hali bir marta ham pul ishlamagan bo‘lsangiz, oyiga $1000 qanday topiladi?
 Vaqtingizni sotishni to‘xtating — natijani soting. Biznes uchun sayt, Telegram-bot, dizayn va Reels yaratishni ko‘rsataman: kechqurunlari, uydan turib, o‘qish bilan birga.
 Kichik buyurtmalardan boshlaysiz, keyin ish narxingiz oshib boradi. Oyiga $300 dan 3–4 ta buyurtma — bu $1000. Daromad harakatlaringizga bog‘liq.
 Telegramdagi bepul mini-kursda — bunga qanday erishish haqida darslar va aniq amaliyot. Aksiya davom etar ekan, kurs to‘liq bepul.
@@ -656,10 +656,10 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>O‘qishni tashlamasdan masofadan ishlab, ota-onangizga o‘zingiz yordam bermoqchimisiz? Mana, noldan oyiga $1000 ga chiqish yo‘li.
+          <t>O‘qishni tashlamasdan masofadan ishlab, ota-onangizga o‘zingiz yordam bermoqchimisiz? Mana, noldan oyiga $1000 topish yo‘li.
 Vaqtingizni sotishni to‘xtating — natijani soting. Biznes uchun sayt, Telegram-bot, dizayn va Reels yaratishni ko‘rsataman: kechqurunlari, uydan turib. Kichik buyurtmalardan boshlaysiz, keyin ish narxingiz oshib boradi. Oyiga $300 dan 3–4 ta buyurtma — bu $1000, bu esa o‘ylaganingizchalik qiyin emas.
 «AI bilan 0 dan ilk $1000 gacha» bepul mini-kursida:
-✅ Nechta buyurtma kerakligini bilasiz: $1000 ga chiqish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
+✅ Nechta buyurtma kerakligini bilasiz: oyiga $1000 topish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
 ✅ Mos xizmatdan boshlaysiz: AI bilan qilinadigan 5 ta xizmatni ko‘rib chiqamiz va sizga qaysi biridan boshlashni maslahat beramiz
 ✅ Faqat ko‘rib o‘tirmaysiz, o‘zingiz qilasiz: amaliy topshiriqda yaqin atrofingizdagi 3 ta kompaniyani topib, ularga sayt yasaysiz
 Faqat bugun, kun oxirigacha, kursdagi joy 3 mln so‘m o‘rniga bepul. Jami 100 ta joy, 74 tasi allaqachon band.
@@ -776,7 +776,7 @@
 Dizayner, montajchi va dasturchi shart emas: siz topshiriq berasiz, AI bajaradi, siz tekshirasiz. AI-mutaxassis shunday ishlaydi.
 «AI bilan 0 dan ilk $1000 gacha» bepul mini-kursida:
 ✅ Qaysi ish uchun to‘lashlarini ko‘rasiz: AI bilan qilinadigan 5 ta xizmatni — sayt, Telegram-bot, dizayn, Reels — ko‘rib chiqamiz va qaysi biridan boshlashni maslahat beramiz
-✅ Nechta buyurtma kerakligini bilasiz: $1000 ga chiqish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
+✅ Nechta buyurtma kerakligini bilasiz: oyiga $1000 topish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
 ✅ Faqat ko‘rib o‘tirmaysiz, o‘zingiz qilasiz: amaliy topshiriqda yaqin atrofingizdagi 3 ta kompaniyani topib, ularga sayt yasaysiz
 ⏳ Kun oxirigacha kurs bepul. 100 ta joydan 26 tasi qoldi.
 👆 «Batafsil» tugmasini bosib, ro‘yxatdan o‘ting.</t>
@@ -811,7 +811,7 @@
       <c r="E8" s="1" t="inlineStr">
         <is>
           <t>«Kun bo‘yi ishlayman, lekin pulim yetmayapti. Qanday qilib ko‘proq pul topsam bo‘ladi?» Vaqtingizni emas, natijani soting. ⏳
-AI bilan ilk $1000 ga qanday chiqishni mini-kursda ko‘rsatamiz — kurs kun oxirigacha bepul. 100 ta joydan 26 tasi qoldi. «Batafsil» tugmasini bosib, ro‘yxatdan o‘ting 👆</t>
+AI bilan ilk $1000 ni qanday topishni mini-kursda ko‘rsatamiz — kurs kun oxirigacha bepul. 100 ta joydan 26 tasi qoldi. «Batafsil» tugmasini bosib, ro‘yxatdan o‘ting 👆</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr"/>
@@ -847,7 +847,7 @@
         <is>
           <t>«Kun bo‘yi ishlayman, lekin pulim yetmayapti. Qanday qilib ko‘proq pul topsam bo‘ladi?» ⏳
 Javobim: vaqtni sotishni to‘xtatib, natijani sotishni boshlash kerak. Ishlagan soat uchun to‘lashsa, daromad soatlar bilan cheklanadi. Tayyor sayt, bot yoki dizayn uchun to‘lashsa — cheklanmaydi, bularni esa kechqurun, uydan turib qilish mumkin.
-Telegramdagi bepul mini-kursda — darslar va amaliyot: AI bilan ilk $1000 ga qanday chiqish, hatto hozir bularning hech birini qilishni bilmasangiz ham.
+Telegramdagi bepul mini-kursda — darslar va amaliyot: AI bilan ilk $1000 ni qanday topish, hatto hozir bularning hech birini qilishni bilmasangiz ham.
 ⏳ Kun oxirigacha kurs bepul. 100 ta joydan 26 tasi qoldi.
 👆 «Batafsil» tugmasini bosib, ro‘yxatdan o‘ting.</t>
         </is>
@@ -892,7 +892,7 @@
 Yechim — vaqtni emas, natijani sotish: biznes uchun sayt, Telegram-bot, dizayn yoki Reels. Toshkentdagi studiyalar oddiy sayt uchun 2,5–5 mln so‘m so‘raydi. Bunday ishni kechqurun, uydan turib, AI yordamida qilish mumkin. Bu — o‘z pulingizni topish yo‘li: ota-onangizdan so‘ramasdan, ularga o‘zingiz yordam berish uchun.
 «AI bilan 0 dan ilk $1000 gacha» bepul mini-kursida:
 ✅ Qaysi ish uchun to‘lashlarini ko‘rasiz: AI bilan qilinadigan 5 ta xizmatni ko‘rib chiqamiz va qaysi biridan boshlashni maslahat beramiz
-✅ Nechta buyurtma kerakligini bilasiz: $1000 ga chiqish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
+✅ Nechta buyurtma kerakligini bilasiz: oyiga $1000 topish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
 ✅ Faqat ko‘rib o‘tirmaysiz, o‘zingiz qilasiz: amaliy topshiriqda yaqin atrofingizdagi 3 ta kompaniyani topib, ularga sayt yasaysiz
 ⏳ Kun oxirigacha kurs bepul. 100 ta joydan 26 tasi qoldi.
 👆 «Batafsil» tugmasini bosib, ro‘yxatdan o‘ting.</t>
@@ -963,7 +963,7 @@
         <is>
           <t>Uydan chiqmasdan qo‘shimcha daromad qilishni xohlaysizmi? ⏳
 Sayt, Telegram-bot, dizayn va Reels uchun biznes pul to‘laydi. Asosiy ishni AI qiladi, siz esa topshiriq berasiz va natijani tekshirasiz: kechqurun, uydan turib, tajribasiz va kodsiz.
-Telegramdagi bepul mini-kursda — darslar va amaliyot: AI bilan ilk $1000 ga qanday chiqish.
+Telegramdagi bepul mini-kursda — darslar va amaliyot: AI bilan ilk $1000 ni qanday topish.
 ⏳ 3 mln o‘rniga 0 so‘m — faqat kun oxirigacha. 100 ta joydan 26 tasi qoldi.
 👆 «Batafsil» tugmasini bosib, ro‘yxatdan o‘ting.</t>
         </is>
@@ -1007,7 +1007,7 @@
 Sayt, Telegram-bot, dizayn va Reels uchun biznes pul to‘laydi. Asosiy ishni AI qiladi, siz esa topshiriq berasiz va natijani tekshirasiz. Buni kechqurunlari, uydan turib, tajribasiz va kodsiz qilish mumkin.
 «AI bilan 0 dan ilk $1000 gacha» bepul mini-kursida:
 ✅ Qaysi ish uchun to‘lashlarini ko‘rasiz: AI bilan qilinadigan 5 ta onlayn xizmatni ko‘rib chiqamiz va qaysi biridan boshlashni maslahat beramiz
-✅ Nechta buyurtma kerakligini bilasiz: $1000 ga chiqish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
+✅ Nechta buyurtma kerakligini bilasiz: oyiga $1000 topish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
 ✅ Amalda sinab ko‘rasiz: amaliy topshiriqda yaqin atrofingizdagi 3 ta kompaniyani topib, ularga sayt yasaysiz
 Oldindan hech narsani bilish shart emas.
 ⏳ 3 mln o‘rniga 0 so‘m — faqat kun oxirigacha. 100 ta joydan 26 tasi qoldi.
@@ -1205,7 +1205,7 @@
         <is>
           <t>O‘qishga ham, asosiy ishga ham xalal bermaydigan qo‘shimcha ish qidiryapsizmi? ⏳
 Zo‘r qo‘shimcha ish — onlayn AI-mutaxassis kasbi. Biznes uchun sayt, Telegram-bot, dizayn va Reels yaratasiz: asosiy ishni AI qiladi, siz esa topshiriq berasiz va natijani tekshirasiz. Uyda noutbuk va haftasiga 2–3 kechqurun yetarli.
-Telegramdagi bepul mini-kursda — noldan darslar va amaliyot: AI bilan ilk $1000 ga qanday chiqish.
+Telegramdagi bepul mini-kursda — noldan darslar va amaliyot: AI bilan ilk $1000 ni qanday topish.
 ⏳ 3 mln o‘rniga 0 so‘m — faqat kun oxirigacha. 100 ta joydan 26 tasi qoldi.
 👆 «Batafsil» tugmasini bosib, ro‘yxatdan o‘ting.</t>
         </is>
@@ -1321,7 +1321,7 @@
         <is>
           <t>Mijoz topishni bilmaysizmi? Xizmatingizni arzonga sotasizmi? ⏳
 Sayt va bot yasashni biladiganlar ko‘p. Pulni esa mijoz topib, munosib narx so‘raydiganlarga to‘lashadi. Mijozni birjasiz izlasa bo‘ladi: shahringizdagi bizneslar orasidan.
-Telegramdagi bepul mini-kursda — ilk $1000 ga chiqish rejasi: nechta buyurtma, qanchadan, mijozni qayerdan izlash. Birinchi dars bilan birga — bonus: bizneslar mutaxassis qidiradigan top-10 kanal.
+Telegramdagi bepul mini-kursda — ilk $1000 ni topish rejasi: nechta buyurtma, qanchadan, mijozni qayerdan izlash. Birinchi dars bilan birga — bonus: bizneslar mutaxassis qidiradigan top-10 kanal.
 ⏳ Kun oxirigacha kurs bepul. 100 ta joydan 26 tasi qoldi.
 👆 «Batafsil» tugmasini bosib, ro‘yxatdan o‘ting.</t>
         </is>
@@ -1365,7 +1365,7 @@
 Sayt yoki bot yasashni biladiganlar ko‘p. Pulni esa mijoz topib, munosib narx so‘raydiganlarga to‘lashadi. Mijoz yo‘q paytda har qanday buyurtmani qancha to‘lashsa, shunga olasiz, daromad esa beqaror: goh deyarli hech narsa, goh yaxshi.
 Yechim — mijozni o‘zingiz, birjasiz izlash: yaqin atrofingizdagi bizneslar orasidan. Toshkentdagi studiyalar oddiy sayt uchun 2,5–5 mln so‘m so‘raydi — narxingiz uchun mo‘ljal shu.
 Bepul mini-kursda:
-✅ Qanday narx so‘rashni bilasiz: $1000 ga chiqish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
+✅ Qanday narx so‘rashni bilasiz: oyiga $1000 topish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
 ✅ Mijozni qayerdan izlashni bilasiz: birinchi dars bilan birga — bonus, bizneslar mutaxassis qidiradigan top-10 kanal
 ✅ Mijozni amalda topasiz: amaliy topshiriqda yaqin atrofingizdagi 3 ta kompaniyani topib, ularga sayt yasaysiz
 ⏳ Kun oxirigacha kurs bepul. 100 ta joydan 26 tasi qoldi.
@@ -1510,13 +1510,13 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Опять «$1000 на ИИ»? Не верь на слово: вот сайт, который я сделал за 2 вечера с ИИ и продал. ⏳
+          <t>Опять «$1000 на ИИ»? Не верь на слово: вот сайт, который я сделал за 2 дня с ИИ и продал. ⏳
 Покажем на бесплатном мини-курсе, как сделать такой же. Вместо 3 млн сум — 0, только до конца дня. Осталось 26 мест из 100. Жми «Подробнее» для регистрации 👆</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>Yana «AI orqali $1000» va’dasimi? Quruq gapga ishonmang: mana bu saytni AI bilan 2 kechqurunda yasadim va sotdim. ⏳
+          <t>Yana «AI orqali $1000» va’dasimi? Quruq gapga ishonmang: mana bu saytni AI bilan 2 kunda yasadim va sotdim. ⏳
 Xuddi shunday saytni qanday yasashni bepul mini-kursda ko‘rsatamiz. 3 mln o‘rniga 0 so‘m — faqat kun oxirigacha. 100 ta joydan 26 tasi qoldi. «Batafsil» tugmasini bosib, ro‘yxatdan o‘ting 👆</t>
         </is>
       </c>
@@ -1543,7 +1543,7 @@
       <c r="D27" s="1" t="inlineStr">
         <is>
           <t>Опять «$1000 на ИИ»? Не верь на слово — смотри, что получилось у меня. ⏳
-Этот сайт я сделал за 2 вечера с нейросетью и продал. Без программирования: я ставил задачу, нейросеть делала, я проверял. Студии Ташкента просят за простой сайт 2,5–5 млн сум.
+Этот сайт я сделал за 2 дня с нейросетью и продал. Без программирования: я ставил задачу, нейросеть делала, я проверял. Студии Ташкента просят за простой сайт 2,5–5 млн сум.
 В бесплатном мини-курсе в Telegram — уроки и практика: покажем, как собрать такой же сайт для компании в твоём районе.
 ⏳ До конца дня курс открыт бесплатно. Осталось 26 мест из 100.
 👆 Жми «Подробнее» для регистрации.</t>
@@ -1552,7 +1552,7 @@
       <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Yana «AI orqali $1000» va’dasimi? Quruq gapga ishonmang — mening natijamni ko‘ring. ⏳
-Bu saytni AI bilan 2 kechqurunda yasadim va sotdim. Kod yozmadim: men topshiriq berdim, AI bajardi, men tekshirdim. Toshkentdagi studiyalar oddiy sayt uchun 2,5–5 mln so‘m so‘raydi.
+Bu saytni AI bilan 2 kunda yasadim va sotdim. Kod yozmadim: men topshiriq berdim, AI bajardi, men tekshirdim. Toshkentdagi studiyalar oddiy sayt uchun 2,5–5 mln so‘m so‘raydi.
 Telegramdagi bepul mini-kursda — darslar va amaliyot: yaqin atrofingizdagi kompaniya uchun xuddi shunday saytni qanday yasashni ko‘rsatamiz.
 ⏳ Kun oxirigacha kurs bepul. 100 ta joydan 26 tasi qoldi.
 👆 «Batafsil» tugmasini bosib, ro‘yxatdan o‘ting.</t>
@@ -1581,7 +1581,7 @@
       <c r="D28" s="1" t="inlineStr">
         <is>
           <t>Опять «$1000 на ИИ»? Не верь на слово — смотри, что получилось у меня. ⏳
-Этот сайт я сделал за 2 вечера с помощью нейросети и продал. Без программирования: я ставил задачу, нейросеть делала, я проверял. Студии Ташкента просят за простой сайт 2,5–5 млн сум.
+Этот сайт я сделал за 2 дня с помощью нейросети и продал. Без программирования: я ставил задачу, нейросеть делала, я проверял. Студии Ташкента просят за простой сайт 2,5–5 млн сум.
 В бесплатном мини-курсе «С 0 до первой $1000 на AI» покажем, как сделать такой же:
 ✅ Видишь, как это устроено: разбираем 5 онлайн-услуг на нейросетях и подсказываем, с какой начать
 ✅ Знаешь, сколько нужно заказов: план выхода на $1000 — сколько заказов, по какой цене, сколько вечеров в неделю
@@ -1593,10 +1593,10 @@
       <c r="E28" s="1" t="inlineStr">
         <is>
           <t>Yana «AI orqali $1000» va’dasimi? Quruq gapga ishonmang — mening natijamni ko‘ring. ⏳
-Bu saytni AI yordamida 2 kechqurunda yasadim va sotdim. Kod yozmadim: men topshiriq berdim, AI bajardi, men tekshirdim. Toshkentdagi studiyalar oddiy sayt uchun 2,5–5 mln so‘m so‘raydi.
+Bu saytni AI yordamida 2 kunda yasadim va sotdim. Kod yozmadim: men topshiriq berdim, AI bajardi, men tekshirdim. Toshkentdagi studiyalar oddiy sayt uchun 2,5–5 mln so‘m so‘raydi.
 «AI bilan 0 dan ilk $1000 gacha» bepul mini-kursida xuddi shunday saytni qanday yasashni ko‘rsatamiz:
 ✅ Bu qanday ishlashini ko‘rasiz: AI bilan qilinadigan 5 ta onlayn xizmatni ko‘rib chiqamiz va qaysi biridan boshlashni maslahat beramiz
-✅ Nechta buyurtma kerakligini bilasiz: $1000 ga chiqish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
+✅ Nechta buyurtma kerakligini bilasiz: oyiga $1000 topish rejasi — nechta buyurtma, qanchadan, haftasiga necha kechqurun
 ✅ O‘zingiz qilasiz: amaliy topshiriqda yaqin atrofingizdagi 3 ta kompaniyani topib, ularga sayt yasaysiz
 ⏳ Kun oxirigacha kurs bepul. 100 ta joydan 26 tasi qoldi.
 👆 «Batafsil» tugmasini bosib, ro‘yxatdan o‘ting.</t>
